--- a/urban_forest_data.xlsx
+++ b/urban_forest_data.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA40"/>
+  <dimension ref="A1:AA41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -640,7 +640,7 @@
         <v>19.32378136608293</v>
       </c>
       <c r="Z2" t="n">
-        <v>0.9307692307692308</v>
+        <v>0.9324999999999999</v>
       </c>
       <c r="AA2" t="n">
         <v>1</v>
@@ -729,7 +729,7 @@
         <v>21.38011662824629</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.8974358974358974</v>
+        <v>0.9</v>
       </c>
       <c r="AA3" t="n">
         <v>2</v>
@@ -818,7 +818,7 @@
         <v>16.53482611266193</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.8358974358974358</v>
+        <v>0.84</v>
       </c>
       <c r="AA4" t="n">
         <v>3</v>
@@ -907,7 +907,7 @@
         <v>19.43787330849897</v>
       </c>
       <c r="Z5" t="n">
-        <v>0.7961538461538461</v>
+        <v>0.80125</v>
       </c>
       <c r="AA5" t="n">
         <v>4</v>
@@ -996,7 +996,7 @@
         <v>19.78383331985661</v>
       </c>
       <c r="Z6" t="n">
-        <v>0.7333333333333333</v>
+        <v>0.7400000000000001</v>
       </c>
       <c r="AA6" t="n">
         <v>5</v>
@@ -1085,7 +1085,7 @@
         <v>20.30289727831431</v>
       </c>
       <c r="Z7" t="n">
-        <v>0.7064102564102565</v>
+        <v>0.7137499999999999</v>
       </c>
       <c r="AA7" t="n">
         <v>6</v>
@@ -1094,12 +1094,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>PTV</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Givatayim</t>
+          <t>Petah Tikva</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1108,73 +1108,73 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>25886</v>
+        <v>65850</v>
       </c>
       <c r="E8" t="n">
-        <v>13323</v>
+        <v>34677</v>
       </c>
       <c r="F8" t="n">
-        <v>1.942955790737822</v>
+        <v>1.898953196643308</v>
       </c>
       <c r="G8" t="n">
-        <v>6.500467434134281</v>
+        <v>6.673055429005315</v>
       </c>
       <c r="H8" t="n">
         <v>6.5</v>
       </c>
       <c r="I8" t="n">
-        <v>2.782661910259416</v>
+        <v>2.349839207564531</v>
       </c>
       <c r="J8" t="n">
-        <v>0.428071048498377</v>
+        <v>0.3521384218315714</v>
       </c>
       <c r="K8" t="n">
-        <v>3.600000000000001</v>
+        <v>3.199999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M8" t="n">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="N8" t="n">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="P8" t="n">
-        <v>13.1</v>
+        <v>13</v>
       </c>
       <c r="Q8" t="n">
-        <v>72.3</v>
+        <v>36.5</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9162077586919779</v>
+        <v>0.6748184525977271</v>
       </c>
       <c r="S8" t="n">
-        <v>39.25537356099822</v>
+        <v>39.30965679574791</v>
       </c>
       <c r="T8" t="n">
-        <v>33.3</v>
+        <v>32.9</v>
       </c>
       <c r="U8" t="n">
-        <v>39.89028818666461</v>
+        <v>39.6826119969628</v>
       </c>
       <c r="V8" t="n">
-        <v>4.690877396862289</v>
+        <v>5.471968160422486</v>
       </c>
       <c r="W8" t="n">
-        <v>4.2</v>
+        <v>4.9</v>
       </c>
       <c r="X8" t="n">
-        <v>10.04403924901491</v>
+        <v>8.669703872437358</v>
       </c>
       <c r="Y8" t="n">
-        <v>18.98709727265704</v>
+        <v>12.87623386484434</v>
       </c>
       <c r="Z8" t="n">
-        <v>0.7025641025641026</v>
+        <v>0.71</v>
       </c>
       <c r="AA8" t="n">
         <v>7</v>
@@ -1183,12 +1183,12 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PTV</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Petah Tikva</t>
+          <t>Givatayim</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1197,73 +1197,73 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>65850</v>
+        <v>25886</v>
       </c>
       <c r="E9" t="n">
-        <v>34677</v>
+        <v>13323</v>
       </c>
       <c r="F9" t="n">
-        <v>1.898953196643308</v>
+        <v>1.942955790737822</v>
       </c>
       <c r="G9" t="n">
-        <v>6.673055429005315</v>
+        <v>6.500467434134281</v>
       </c>
       <c r="H9" t="n">
         <v>6.5</v>
       </c>
       <c r="I9" t="n">
-        <v>2.349839207564531</v>
+        <v>2.782661910259416</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3521384218315714</v>
+        <v>0.428071048498377</v>
       </c>
       <c r="K9" t="n">
-        <v>3.199999999999999</v>
+        <v>3.600000000000001</v>
       </c>
       <c r="L9" t="n">
-        <v>3.6</v>
+        <v>2.6</v>
       </c>
       <c r="M9" t="n">
-        <v>5</v>
+        <v>4.7</v>
       </c>
       <c r="N9" t="n">
-        <v>8.199999999999999</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="O9" t="n">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="P9" t="n">
-        <v>13</v>
+        <v>13.1</v>
       </c>
       <c r="Q9" t="n">
-        <v>36.5</v>
+        <v>72.3</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6748184525977271</v>
+        <v>0.9162077586919779</v>
       </c>
       <c r="S9" t="n">
-        <v>39.30965679574791</v>
+        <v>39.25537356099822</v>
       </c>
       <c r="T9" t="n">
-        <v>32.9</v>
+        <v>33.3</v>
       </c>
       <c r="U9" t="n">
-        <v>39.6826119969628</v>
+        <v>39.89028818666461</v>
       </c>
       <c r="V9" t="n">
-        <v>5.471968160422486</v>
+        <v>4.690877396862289</v>
       </c>
       <c r="W9" t="n">
-        <v>4.9</v>
+        <v>4.2</v>
       </c>
       <c r="X9" t="n">
-        <v>8.669703872437358</v>
+        <v>10.04403924901491</v>
       </c>
       <c r="Y9" t="n">
-        <v>12.87623386484434</v>
+        <v>18.98709727265704</v>
       </c>
       <c r="Z9" t="n">
-        <v>0.7025641025641026</v>
+        <v>0.71</v>
       </c>
       <c r="AA9" t="n">
         <v>7</v>
@@ -1352,7 +1352,7 @@
         <v>11.21200513733354</v>
       </c>
       <c r="Z10" t="n">
-        <v>0.6666666666666666</v>
+        <v>0.675</v>
       </c>
       <c r="AA10" t="n">
         <v>9</v>
@@ -1441,7 +1441,7 @@
         <v>15.24941255454851</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.6564102564102565</v>
+        <v>0.665</v>
       </c>
       <c r="AA11" t="n">
         <v>10</v>
@@ -1530,7 +1530,7 @@
         <v>18.24967310765654</v>
       </c>
       <c r="Z12" t="n">
-        <v>0.6384615384615385</v>
+        <v>0.6475</v>
       </c>
       <c r="AA12" t="n">
         <v>11</v>
@@ -1619,7 +1619,7 @@
         <v>15.29671120709047</v>
       </c>
       <c r="Z13" t="n">
-        <v>0.5884615384615384</v>
+        <v>0.59875</v>
       </c>
       <c r="AA13" t="n">
         <v>12</v>
@@ -1708,7 +1708,7 @@
         <v>10.69077086680091</v>
       </c>
       <c r="Z14" t="n">
-        <v>0.5858974358974358</v>
+        <v>0.5925</v>
       </c>
       <c r="AA14" t="n">
         <v>13</v>
@@ -1797,7 +1797,7 @@
         <v>26.29187933676208</v>
       </c>
       <c r="Z15" t="n">
-        <v>0.5705128205128205</v>
+        <v>0.58125</v>
       </c>
       <c r="AA15" t="n">
         <v>14</v>
@@ -1886,7 +1886,7 @@
         <v>24.06150088012357</v>
       </c>
       <c r="Z16" t="n">
-        <v>0.555128205128205</v>
+        <v>0.56625</v>
       </c>
       <c r="AA16" t="n">
         <v>15</v>
@@ -1975,7 +1975,7 @@
         <v>27.69957365480741</v>
       </c>
       <c r="Z17" t="n">
-        <v>0.5538461538461539</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="AA17" t="n">
         <v>16</v>
@@ -2064,7 +2064,7 @@
         <v>17.51395827211284</v>
       </c>
       <c r="Z18" t="n">
-        <v>0.5448717948717949</v>
+        <v>0.55625</v>
       </c>
       <c r="AA18" t="n">
         <v>17</v>
@@ -2153,7 +2153,7 @@
         <v>14.54400319297545</v>
       </c>
       <c r="Z19" t="n">
-        <v>0.5435897435897437</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="AA19" t="n">
         <v>18</v>
@@ -2242,7 +2242,7 @@
         <v>14.46076506166051</v>
       </c>
       <c r="Z20" t="n">
-        <v>0.5179487179487179</v>
+        <v>0.53</v>
       </c>
       <c r="AA20" t="n">
         <v>19</v>
@@ -2331,7 +2331,7 @@
         <v>34.20768656096953</v>
       </c>
       <c r="Z21" t="n">
-        <v>0.4948717948717948</v>
+        <v>0.5075</v>
       </c>
       <c r="AA21" t="n">
         <v>20</v>
@@ -2420,7 +2420,7 @@
         <v>31.53048225659691</v>
       </c>
       <c r="Z22" t="n">
-        <v>0.4756410256410257</v>
+        <v>0.48875</v>
       </c>
       <c r="AA22" t="n">
         <v>21</v>
@@ -2509,7 +2509,7 @@
         <v>18.16864939250729</v>
       </c>
       <c r="Z23" t="n">
-        <v>0.4743589743589744</v>
+        <v>0.4875</v>
       </c>
       <c r="AA23" t="n">
         <v>22</v>
@@ -2598,7 +2598,7 @@
         <v>13.7958208661175</v>
       </c>
       <c r="Z24" t="n">
-        <v>0.4705128205128205</v>
+        <v>0.48375</v>
       </c>
       <c r="AA24" t="n">
         <v>23</v>
@@ -2687,7 +2687,7 @@
         <v>28.73426247344697</v>
       </c>
       <c r="Z25" t="n">
-        <v>0.441025641025641</v>
+        <v>0.455</v>
       </c>
       <c r="AA25" t="n">
         <v>24</v>
@@ -2776,7 +2776,7 @@
         <v>34.07683515583685</v>
       </c>
       <c r="Z26" t="n">
-        <v>0.4179487179487179</v>
+        <v>0.4324999999999999</v>
       </c>
       <c r="AA26" t="n">
         <v>25</v>
@@ -2865,7 +2865,7 @@
         <v>30.59088767750185</v>
       </c>
       <c r="Z27" t="n">
-        <v>0.4012820512820512</v>
+        <v>0.41625</v>
       </c>
       <c r="AA27" t="n">
         <v>26</v>
@@ -2954,7 +2954,7 @@
         <v>26.93861541478721</v>
       </c>
       <c r="Z28" t="n">
-        <v>0.3884615384615385</v>
+        <v>0.4037500000000001</v>
       </c>
       <c r="AA28" t="n">
         <v>27</v>
@@ -3043,7 +3043,7 @@
         <v>15.78086445424048</v>
       </c>
       <c r="Z29" t="n">
-        <v>0.3858974358974359</v>
+        <v>0.3975</v>
       </c>
       <c r="AA29" t="n">
         <v>28</v>
@@ -3132,7 +3132,7 @@
         <v>30.63396383288298</v>
       </c>
       <c r="Z30" t="n">
-        <v>0.3769230769230769</v>
+        <v>0.3925</v>
       </c>
       <c r="AA30" t="n">
         <v>29</v>
@@ -3221,7 +3221,7 @@
         <v>29.53845923418532</v>
       </c>
       <c r="Z31" t="n">
-        <v>0.35</v>
+        <v>0.36625</v>
       </c>
       <c r="AA31" t="n">
         <v>30</v>
@@ -3310,7 +3310,7 @@
         <v>29.89699149771092</v>
       </c>
       <c r="Z32" t="n">
-        <v>0.3461538461538462</v>
+        <v>0.3625</v>
       </c>
       <c r="AA32" t="n">
         <v>31</v>
@@ -3399,7 +3399,7 @@
         <v>32.02979014872312</v>
       </c>
       <c r="Z33" t="n">
-        <v>0.3397435897435898</v>
+        <v>0.35625</v>
       </c>
       <c r="AA33" t="n">
         <v>32</v>
@@ -3488,7 +3488,7 @@
         <v>35.20908301278074</v>
       </c>
       <c r="Z34" t="n">
-        <v>0.3294871794871794</v>
+        <v>0.3462499999999999</v>
       </c>
       <c r="AA34" t="n">
         <v>33</v>
@@ -3577,7 +3577,7 @@
         <v>33.95124135241699</v>
       </c>
       <c r="Z35" t="n">
-        <v>0.3282051282051281</v>
+        <v>0.345</v>
       </c>
       <c r="AA35" t="n">
         <v>34</v>
@@ -3666,7 +3666,7 @@
         <v>18.92590968873301</v>
       </c>
       <c r="Z36" t="n">
-        <v>0.2807692307692308</v>
+        <v>0.2987500000000001</v>
       </c>
       <c r="AA36" t="n">
         <v>35</v>
@@ -3755,7 +3755,7 @@
         <v>18.98979363778589</v>
       </c>
       <c r="Z37" t="n">
-        <v>0.2769230769230769</v>
+        <v>0.295</v>
       </c>
       <c r="AA37" t="n">
         <v>36</v>
@@ -3844,7 +3844,7 @@
         <v>15.27473358022825</v>
       </c>
       <c r="Z38" t="n">
-        <v>0.2730769230769231</v>
+        <v>0.2875</v>
       </c>
       <c r="AA38" t="n">
         <v>37</v>
@@ -3933,7 +3933,7 @@
         <v>16.48348274591674</v>
       </c>
       <c r="Z39" t="n">
-        <v>0.2615384615384616</v>
+        <v>0.2762500000000001</v>
       </c>
       <c r="AA39" t="n">
         <v>38</v>
@@ -4022,10 +4022,99 @@
         <v>36.61107702604718</v>
       </c>
       <c r="Z40" t="n">
-        <v>0.1602564102564102</v>
+        <v>0.17625</v>
       </c>
       <c r="AA40" t="n">
         <v>39</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>BTR</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Beitar Ilit</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>13289</v>
+      </c>
+      <c r="E41" t="n">
+        <v>9911</v>
+      </c>
+      <c r="F41" t="n">
+        <v>1.340833417414993</v>
+      </c>
+      <c r="G41" t="n">
+        <v>5.075611407931371</v>
+      </c>
+      <c r="H41" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="I41" t="n">
+        <v>1.743597247380789</v>
+      </c>
+      <c r="J41" t="n">
+        <v>0.343524574134294</v>
+      </c>
+      <c r="K41" t="n">
+        <v>2.399999999999999</v>
+      </c>
+      <c r="L41" t="n">
+        <v>3</v>
+      </c>
+      <c r="M41" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N41" t="n">
+        <v>6.1</v>
+      </c>
+      <c r="O41" t="n">
+        <v>7.3</v>
+      </c>
+      <c r="P41" t="n">
+        <v>10.3</v>
+      </c>
+      <c r="Q41" t="n">
+        <v>13.7</v>
+      </c>
+      <c r="R41" t="n">
+        <v>0.9196970934647821</v>
+      </c>
+      <c r="S41" t="n">
+        <v>22.62577319587629</v>
+      </c>
+      <c r="T41" t="n">
+        <v>18.9</v>
+      </c>
+      <c r="U41" t="n">
+        <v>64.48942734592519</v>
+      </c>
+      <c r="V41" t="n">
+        <v>4.570723453908985</v>
+      </c>
+      <c r="W41" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="X41" t="n">
+        <v>1.354503724885243</v>
+      </c>
+      <c r="Y41" t="n">
+        <v>29.38520580931597</v>
+      </c>
+      <c r="Z41" t="n">
+        <v>0.045</v>
+      </c>
+      <c r="AA41" t="n">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -4039,7 +4128,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O40"/>
+  <dimension ref="A1:O41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4479,814 +4568,814 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTY</t>
+          <t>BTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bat Yam</t>
+          <t>Beitar Ilit</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3065</v>
+        <v>0</v>
       </c>
       <c r="D9" t="n">
-        <v>3107</v>
+        <v>1282</v>
       </c>
       <c r="E9" t="n">
-        <v>2491</v>
+        <v>2623</v>
       </c>
       <c r="F9" t="n">
-        <v>2571</v>
+        <v>2905</v>
       </c>
       <c r="G9" t="n">
-        <v>3137</v>
+        <v>2857</v>
       </c>
       <c r="H9" t="n">
-        <v>3618</v>
+        <v>1923</v>
       </c>
       <c r="I9" t="n">
-        <v>3172</v>
+        <v>801</v>
       </c>
       <c r="J9" t="n">
-        <v>2433</v>
+        <v>488</v>
       </c>
       <c r="K9" t="n">
-        <v>1877</v>
+        <v>230</v>
       </c>
       <c r="L9" t="n">
-        <v>1615</v>
+        <v>151</v>
       </c>
       <c r="M9" t="n">
-        <v>351</v>
+        <v>29</v>
       </c>
       <c r="N9" t="n">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="O9" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>BTY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eilat</t>
+          <t>Bat Yam</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0</v>
+        <v>3065</v>
       </c>
       <c r="D10" t="n">
-        <v>827</v>
+        <v>3107</v>
       </c>
       <c r="E10" t="n">
-        <v>1722</v>
+        <v>2491</v>
       </c>
       <c r="F10" t="n">
-        <v>1999</v>
+        <v>2571</v>
       </c>
       <c r="G10" t="n">
-        <v>2495</v>
+        <v>3137</v>
       </c>
       <c r="H10" t="n">
-        <v>2332</v>
+        <v>3618</v>
       </c>
       <c r="I10" t="n">
-        <v>1570</v>
+        <v>3172</v>
       </c>
       <c r="J10" t="n">
-        <v>1158</v>
+        <v>2433</v>
       </c>
       <c r="K10" t="n">
-        <v>626</v>
+        <v>1877</v>
       </c>
       <c r="L10" t="n">
-        <v>595</v>
+        <v>1615</v>
       </c>
       <c r="M10" t="n">
-        <v>99</v>
+        <v>351</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>ELT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Givatayim</t>
+          <t>Eilat</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>1445</v>
+        <v>0</v>
       </c>
       <c r="D11" t="n">
-        <v>1717</v>
+        <v>827</v>
       </c>
       <c r="E11" t="n">
-        <v>1753</v>
+        <v>1722</v>
       </c>
       <c r="F11" t="n">
-        <v>2150</v>
+        <v>1999</v>
       </c>
       <c r="G11" t="n">
-        <v>3498</v>
+        <v>2495</v>
       </c>
       <c r="H11" t="n">
-        <v>4215</v>
+        <v>2332</v>
       </c>
       <c r="I11" t="n">
-        <v>3652</v>
+        <v>1570</v>
       </c>
       <c r="J11" t="n">
-        <v>2962</v>
+        <v>1158</v>
       </c>
       <c r="K11" t="n">
-        <v>1894</v>
+        <v>626</v>
       </c>
       <c r="L11" t="n">
-        <v>1971</v>
+        <v>595</v>
       </c>
       <c r="M11" t="n">
-        <v>536</v>
+        <v>99</v>
       </c>
       <c r="N11" t="n">
-        <v>69</v>
+        <v>0</v>
       </c>
       <c r="O11" t="n">
-        <v>21</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAI</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Givatayim</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>16308</v>
+        <v>1445</v>
       </c>
       <c r="D12" t="n">
-        <v>15852</v>
+        <v>1717</v>
       </c>
       <c r="E12" t="n">
-        <v>13722</v>
+        <v>1753</v>
       </c>
       <c r="F12" t="n">
-        <v>16219</v>
+        <v>2150</v>
       </c>
       <c r="G12" t="n">
-        <v>24695</v>
+        <v>3498</v>
       </c>
       <c r="H12" t="n">
-        <v>32486</v>
+        <v>4215</v>
       </c>
       <c r="I12" t="n">
-        <v>30928</v>
+        <v>3652</v>
       </c>
       <c r="J12" t="n">
-        <v>27316</v>
+        <v>2962</v>
       </c>
       <c r="K12" t="n">
-        <v>24548</v>
+        <v>1894</v>
       </c>
       <c r="L12" t="n">
-        <v>19950</v>
+        <v>1971</v>
       </c>
       <c r="M12" t="n">
-        <v>14553</v>
+        <v>536</v>
       </c>
       <c r="N12" t="n">
-        <v>744</v>
+        <v>69</v>
       </c>
       <c r="O12" t="n">
-        <v>61</v>
+        <v>21</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>HAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hadera</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>6596</v>
+        <v>16308</v>
       </c>
       <c r="D13" t="n">
-        <v>7139</v>
+        <v>15852</v>
       </c>
       <c r="E13" t="n">
-        <v>7711</v>
+        <v>13722</v>
       </c>
       <c r="F13" t="n">
-        <v>10599</v>
+        <v>16219</v>
       </c>
       <c r="G13" t="n">
-        <v>16405</v>
+        <v>24695</v>
       </c>
       <c r="H13" t="n">
-        <v>15676</v>
+        <v>32486</v>
       </c>
       <c r="I13" t="n">
-        <v>12705</v>
+        <v>30928</v>
       </c>
       <c r="J13" t="n">
-        <v>11039</v>
+        <v>27316</v>
       </c>
       <c r="K13" t="n">
-        <v>7348</v>
+        <v>24548</v>
       </c>
       <c r="L13" t="n">
-        <v>10169</v>
+        <v>19950</v>
       </c>
       <c r="M13" t="n">
-        <v>4140</v>
+        <v>14553</v>
       </c>
       <c r="N13" t="n">
-        <v>540</v>
+        <v>744</v>
       </c>
       <c r="O13" t="n">
-        <v>208</v>
+        <v>61</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HDS</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hod HaSharon</t>
+          <t>Hadera</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0</v>
+        <v>6596</v>
       </c>
       <c r="D14" t="n">
-        <v>1467</v>
+        <v>7139</v>
       </c>
       <c r="E14" t="n">
-        <v>3258</v>
+        <v>7711</v>
       </c>
       <c r="F14" t="n">
-        <v>4058</v>
+        <v>10599</v>
       </c>
       <c r="G14" t="n">
-        <v>6796</v>
+        <v>16405</v>
       </c>
       <c r="H14" t="n">
-        <v>9757</v>
+        <v>15676</v>
       </c>
       <c r="I14" t="n">
-        <v>7681</v>
+        <v>12705</v>
       </c>
       <c r="J14" t="n">
-        <v>5474</v>
+        <v>11039</v>
       </c>
       <c r="K14" t="n">
-        <v>2733</v>
+        <v>7348</v>
       </c>
       <c r="L14" t="n">
-        <v>2299</v>
+        <v>10169</v>
       </c>
       <c r="M14" t="n">
-        <v>578</v>
+        <v>4140</v>
       </c>
       <c r="N14" t="n">
-        <v>87</v>
+        <v>540</v>
       </c>
       <c r="O14" t="n">
-        <v>9</v>
+        <v>208</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HOL</t>
+          <t>HDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Holon</t>
+          <t>Hod HaSharon</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>5237</v>
+        <v>0</v>
       </c>
       <c r="D15" t="n">
-        <v>5190</v>
+        <v>1467</v>
       </c>
       <c r="E15" t="n">
-        <v>4646</v>
+        <v>3258</v>
       </c>
       <c r="F15" t="n">
-        <v>5322</v>
+        <v>4058</v>
       </c>
       <c r="G15" t="n">
-        <v>6960</v>
+        <v>6796</v>
       </c>
       <c r="H15" t="n">
-        <v>7230</v>
+        <v>9757</v>
       </c>
       <c r="I15" t="n">
-        <v>6471</v>
+        <v>7681</v>
       </c>
       <c r="J15" t="n">
-        <v>5543</v>
+        <v>5474</v>
       </c>
       <c r="K15" t="n">
-        <v>3928</v>
+        <v>2733</v>
       </c>
       <c r="L15" t="n">
-        <v>3058</v>
+        <v>2299</v>
       </c>
       <c r="M15" t="n">
-        <v>830</v>
+        <v>578</v>
       </c>
       <c r="N15" t="n">
-        <v>0</v>
+        <v>87</v>
       </c>
       <c r="O15" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HRZ</t>
+          <t>HOL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Herzliya</t>
+          <t>Holon</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>5068</v>
+        <v>5237</v>
       </c>
       <c r="D16" t="n">
-        <v>4999</v>
+        <v>5190</v>
       </c>
       <c r="E16" t="n">
-        <v>4613</v>
+        <v>4646</v>
       </c>
       <c r="F16" t="n">
-        <v>5637</v>
+        <v>5322</v>
       </c>
       <c r="G16" t="n">
-        <v>9532</v>
+        <v>6960</v>
       </c>
       <c r="H16" t="n">
-        <v>12950</v>
+        <v>7230</v>
       </c>
       <c r="I16" t="n">
-        <v>11833</v>
+        <v>6471</v>
       </c>
       <c r="J16" t="n">
-        <v>8683</v>
+        <v>5543</v>
       </c>
       <c r="K16" t="n">
-        <v>5056</v>
+        <v>3928</v>
       </c>
       <c r="L16" t="n">
-        <v>4287</v>
+        <v>3058</v>
       </c>
       <c r="M16" t="n">
-        <v>1410</v>
+        <v>830</v>
       </c>
       <c r="N16" t="n">
-        <v>105</v>
+        <v>0</v>
       </c>
       <c r="O16" t="n">
-        <v>26</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JER</t>
+          <t>HRZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Herzliya</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>51995</v>
+        <v>5068</v>
       </c>
       <c r="D17" t="n">
-        <v>53831</v>
+        <v>4999</v>
       </c>
       <c r="E17" t="n">
-        <v>48957</v>
+        <v>4613</v>
       </c>
       <c r="F17" t="n">
-        <v>53874</v>
+        <v>5637</v>
       </c>
       <c r="G17" t="n">
-        <v>70241</v>
+        <v>9532</v>
       </c>
       <c r="H17" t="n">
-        <v>72217</v>
+        <v>12950</v>
       </c>
       <c r="I17" t="n">
-        <v>58959</v>
+        <v>11833</v>
       </c>
       <c r="J17" t="n">
-        <v>40001</v>
+        <v>8683</v>
       </c>
       <c r="K17" t="n">
-        <v>18576</v>
+        <v>5056</v>
       </c>
       <c r="L17" t="n">
-        <v>11996</v>
+        <v>4287</v>
       </c>
       <c r="M17" t="n">
-        <v>2589</v>
+        <v>1410</v>
       </c>
       <c r="N17" t="n">
-        <v>11</v>
+        <v>105</v>
       </c>
       <c r="O17" t="n">
-        <v>0</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAT</t>
+          <t>JER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kiryat Ata</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>1625</v>
+        <v>51995</v>
       </c>
       <c r="D18" t="n">
-        <v>3334</v>
+        <v>53831</v>
       </c>
       <c r="E18" t="n">
-        <v>5090</v>
+        <v>48957</v>
       </c>
       <c r="F18" t="n">
-        <v>6017</v>
+        <v>53874</v>
       </c>
       <c r="G18" t="n">
-        <v>8488</v>
+        <v>70241</v>
       </c>
       <c r="H18" t="n">
-        <v>9228</v>
+        <v>72217</v>
       </c>
       <c r="I18" t="n">
-        <v>7625</v>
+        <v>58959</v>
       </c>
       <c r="J18" t="n">
-        <v>5871</v>
+        <v>40001</v>
       </c>
       <c r="K18" t="n">
-        <v>3469</v>
+        <v>18576</v>
       </c>
       <c r="L18" t="n">
-        <v>2892</v>
+        <v>11996</v>
       </c>
       <c r="M18" t="n">
-        <v>1110</v>
+        <v>2589</v>
       </c>
       <c r="N18" t="n">
-        <v>260</v>
+        <v>11</v>
       </c>
       <c r="O18" t="n">
-        <v>55</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KFS</t>
+          <t>KAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kfar Saba</t>
+          <t>Kiryat Ata</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>3698</v>
+        <v>1625</v>
       </c>
       <c r="D19" t="n">
-        <v>3864</v>
+        <v>3334</v>
       </c>
       <c r="E19" t="n">
-        <v>3538</v>
+        <v>5090</v>
       </c>
       <c r="F19" t="n">
-        <v>4335</v>
+        <v>6017</v>
       </c>
       <c r="G19" t="n">
-        <v>6949</v>
+        <v>8488</v>
       </c>
       <c r="H19" t="n">
-        <v>9654</v>
+        <v>9228</v>
       </c>
       <c r="I19" t="n">
-        <v>8539</v>
+        <v>7625</v>
       </c>
       <c r="J19" t="n">
-        <v>5912</v>
+        <v>5871</v>
       </c>
       <c r="K19" t="n">
-        <v>3890</v>
+        <v>3469</v>
       </c>
       <c r="L19" t="n">
-        <v>2996</v>
+        <v>2892</v>
       </c>
       <c r="M19" t="n">
-        <v>1099</v>
+        <v>1110</v>
       </c>
       <c r="N19" t="n">
-        <v>179</v>
+        <v>260</v>
       </c>
       <c r="O19" t="n">
-        <v>14</v>
+        <v>55</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KGT</t>
+          <t>KFS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kiryat Gat</t>
+          <t>Kfar Saba</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>2955</v>
+        <v>3698</v>
       </c>
       <c r="D20" t="n">
-        <v>3177</v>
+        <v>3864</v>
       </c>
       <c r="E20" t="n">
-        <v>2959</v>
+        <v>3538</v>
       </c>
       <c r="F20" t="n">
-        <v>3443</v>
+        <v>4335</v>
       </c>
       <c r="G20" t="n">
-        <v>4259</v>
+        <v>6949</v>
       </c>
       <c r="H20" t="n">
-        <v>3778</v>
+        <v>9654</v>
       </c>
       <c r="I20" t="n">
-        <v>2797</v>
+        <v>8539</v>
       </c>
       <c r="J20" t="n">
-        <v>1994</v>
+        <v>5912</v>
       </c>
       <c r="K20" t="n">
-        <v>2267</v>
+        <v>3890</v>
       </c>
       <c r="L20" t="n">
-        <v>1803</v>
+        <v>2996</v>
       </c>
       <c r="M20" t="n">
-        <v>237</v>
+        <v>1099</v>
       </c>
       <c r="N20" t="n">
-        <v>45</v>
+        <v>179</v>
       </c>
       <c r="O20" t="n">
-        <v>4</v>
+        <v>14</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOD</t>
+          <t>KGT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lod</t>
+          <t>Kiryat Gat</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>3672</v>
+        <v>2955</v>
       </c>
       <c r="D21" t="n">
-        <v>3853</v>
+        <v>3177</v>
       </c>
       <c r="E21" t="n">
-        <v>3446</v>
+        <v>2959</v>
       </c>
       <c r="F21" t="n">
-        <v>4133</v>
+        <v>3443</v>
       </c>
       <c r="G21" t="n">
-        <v>5563</v>
+        <v>4259</v>
       </c>
       <c r="H21" t="n">
-        <v>5516</v>
+        <v>3778</v>
       </c>
       <c r="I21" t="n">
-        <v>3974</v>
+        <v>2797</v>
       </c>
       <c r="J21" t="n">
-        <v>2805</v>
+        <v>1994</v>
       </c>
       <c r="K21" t="n">
-        <v>1794</v>
+        <v>2267</v>
       </c>
       <c r="L21" t="n">
-        <v>1531</v>
+        <v>1803</v>
       </c>
       <c r="M21" t="n">
-        <v>391</v>
+        <v>237</v>
       </c>
       <c r="N21" t="n">
-        <v>18</v>
+        <v>45</v>
       </c>
       <c r="O21" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MDN</t>
+          <t>LOD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modiin</t>
+          <t>Lod</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>6</v>
+        <v>3672</v>
       </c>
       <c r="D22" t="n">
-        <v>3504</v>
+        <v>3853</v>
       </c>
       <c r="E22" t="n">
-        <v>7874</v>
+        <v>3446</v>
       </c>
       <c r="F22" t="n">
-        <v>9271</v>
+        <v>4133</v>
       </c>
       <c r="G22" t="n">
-        <v>13938</v>
+        <v>5563</v>
       </c>
       <c r="H22" t="n">
-        <v>14682</v>
+        <v>5516</v>
       </c>
       <c r="I22" t="n">
-        <v>10152</v>
+        <v>3974</v>
       </c>
       <c r="J22" t="n">
-        <v>6163</v>
+        <v>2805</v>
       </c>
       <c r="K22" t="n">
-        <v>3430</v>
+        <v>1794</v>
       </c>
       <c r="L22" t="n">
-        <v>2711</v>
+        <v>1531</v>
       </c>
       <c r="M22" t="n">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="N22" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
       <c r="O22" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NHR</t>
+          <t>MDN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nahariya</t>
+          <t>Modiin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="D23" t="n">
-        <v>1029</v>
+        <v>3504</v>
       </c>
       <c r="E23" t="n">
-        <v>2371</v>
+        <v>7874</v>
       </c>
       <c r="F23" t="n">
-        <v>2792</v>
+        <v>9271</v>
       </c>
       <c r="G23" t="n">
-        <v>3650</v>
+        <v>13938</v>
       </c>
       <c r="H23" t="n">
-        <v>3804</v>
+        <v>14682</v>
       </c>
       <c r="I23" t="n">
-        <v>3089</v>
+        <v>10152</v>
       </c>
       <c r="J23" t="n">
-        <v>2046</v>
+        <v>6163</v>
       </c>
       <c r="K23" t="n">
-        <v>1496</v>
+        <v>3430</v>
       </c>
       <c r="L23" t="n">
-        <v>1587</v>
+        <v>2711</v>
       </c>
       <c r="M23" t="n">
-        <v>293</v>
+        <v>387</v>
       </c>
       <c r="N23" t="n">
-        <v>70</v>
+        <v>14</v>
       </c>
       <c r="O23" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NSZ</t>
+          <t>NHR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Ziona</t>
+          <t>Nahariya</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>0</v>
       </c>
       <c r="D24" t="n">
-        <v>1842</v>
+        <v>1029</v>
       </c>
       <c r="E24" t="n">
-        <v>4221</v>
+        <v>2371</v>
       </c>
       <c r="F24" t="n">
-        <v>5968</v>
+        <v>2792</v>
       </c>
       <c r="G24" t="n">
-        <v>8763</v>
+        <v>3650</v>
       </c>
       <c r="H24" t="n">
-        <v>7793</v>
+        <v>3804</v>
       </c>
       <c r="I24" t="n">
-        <v>4674</v>
+        <v>3089</v>
       </c>
       <c r="J24" t="n">
-        <v>3159</v>
+        <v>2046</v>
       </c>
       <c r="K24" t="n">
-        <v>1609</v>
+        <v>1496</v>
       </c>
       <c r="L24" t="n">
-        <v>1361</v>
+        <v>1587</v>
       </c>
       <c r="M24" t="n">
-        <v>298</v>
+        <v>293</v>
       </c>
       <c r="N24" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="O24" t="n">
         <v>0</v>
@@ -5295,610 +5384,610 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NTN</t>
+          <t>NSZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Netanya</t>
+          <t>Ness Ziona</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>0</v>
       </c>
       <c r="D25" t="n">
-        <v>3609</v>
+        <v>1842</v>
       </c>
       <c r="E25" t="n">
-        <v>7748</v>
+        <v>4221</v>
       </c>
       <c r="F25" t="n">
-        <v>9052</v>
+        <v>5968</v>
       </c>
       <c r="G25" t="n">
-        <v>12895</v>
+        <v>8763</v>
       </c>
       <c r="H25" t="n">
-        <v>13638</v>
+        <v>7793</v>
       </c>
       <c r="I25" t="n">
-        <v>10036</v>
+        <v>4674</v>
       </c>
       <c r="J25" t="n">
-        <v>7170</v>
+        <v>3159</v>
       </c>
       <c r="K25" t="n">
-        <v>4364</v>
+        <v>1609</v>
       </c>
       <c r="L25" t="n">
-        <v>4256</v>
+        <v>1361</v>
       </c>
       <c r="M25" t="n">
-        <v>1412</v>
+        <v>298</v>
       </c>
       <c r="N25" t="n">
-        <v>258</v>
+        <v>5</v>
       </c>
       <c r="O25" t="n">
-        <v>37</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NTV</t>
+          <t>NTN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Netivot</t>
+          <t>Netanya</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>1943</v>
+        <v>0</v>
       </c>
       <c r="D26" t="n">
-        <v>2011</v>
+        <v>3609</v>
       </c>
       <c r="E26" t="n">
-        <v>1721</v>
+        <v>7748</v>
       </c>
       <c r="F26" t="n">
-        <v>1825</v>
+        <v>9052</v>
       </c>
       <c r="G26" t="n">
-        <v>1957</v>
+        <v>12895</v>
       </c>
       <c r="H26" t="n">
-        <v>1929</v>
+        <v>13638</v>
       </c>
       <c r="I26" t="n">
-        <v>1633</v>
+        <v>10036</v>
       </c>
       <c r="J26" t="n">
-        <v>1261</v>
+        <v>7170</v>
       </c>
       <c r="K26" t="n">
-        <v>805</v>
+        <v>4364</v>
       </c>
       <c r="L26" t="n">
-        <v>740</v>
+        <v>4256</v>
       </c>
       <c r="M26" t="n">
-        <v>274</v>
+        <v>1412</v>
       </c>
       <c r="N26" t="n">
-        <v>19</v>
+        <v>258</v>
       </c>
       <c r="O26" t="n">
-        <v>0</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NZR</t>
+          <t>NTV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nazareth</t>
+          <t>Netivot</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>785</v>
+        <v>1943</v>
       </c>
       <c r="D27" t="n">
-        <v>2757</v>
+        <v>2011</v>
       </c>
       <c r="E27" t="n">
-        <v>5092</v>
+        <v>1721</v>
       </c>
       <c r="F27" t="n">
-        <v>6536</v>
+        <v>1825</v>
       </c>
       <c r="G27" t="n">
-        <v>9287</v>
+        <v>1957</v>
       </c>
       <c r="H27" t="n">
-        <v>9086</v>
+        <v>1929</v>
       </c>
       <c r="I27" t="n">
-        <v>5815</v>
+        <v>1633</v>
       </c>
       <c r="J27" t="n">
-        <v>3052</v>
+        <v>1261</v>
       </c>
       <c r="K27" t="n">
-        <v>1816</v>
+        <v>805</v>
       </c>
       <c r="L27" t="n">
-        <v>1095</v>
+        <v>740</v>
       </c>
       <c r="M27" t="n">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="N27" t="n">
         <v>19</v>
       </c>
       <c r="O27" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PHK</t>
+          <t>NZR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pardes Hanna-Karkur</t>
+          <t>Nazareth</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>5</v>
+        <v>785</v>
       </c>
       <c r="D28" t="n">
-        <v>1569</v>
+        <v>2757</v>
       </c>
       <c r="E28" t="n">
-        <v>3402</v>
+        <v>5092</v>
       </c>
       <c r="F28" t="n">
-        <v>4485</v>
+        <v>6536</v>
       </c>
       <c r="G28" t="n">
-        <v>6617</v>
+        <v>9287</v>
       </c>
       <c r="H28" t="n">
-        <v>8795</v>
+        <v>9086</v>
       </c>
       <c r="I28" t="n">
-        <v>7227</v>
+        <v>5815</v>
       </c>
       <c r="J28" t="n">
-        <v>5531</v>
+        <v>3052</v>
       </c>
       <c r="K28" t="n">
-        <v>3441</v>
+        <v>1816</v>
       </c>
       <c r="L28" t="n">
-        <v>2434</v>
+        <v>1095</v>
       </c>
       <c r="M28" t="n">
-        <v>688</v>
+        <v>272</v>
       </c>
       <c r="N28" t="n">
-        <v>131</v>
+        <v>19</v>
       </c>
       <c r="O28" t="n">
-        <v>27</v>
+        <v>8</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTV</t>
+          <t>PHK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Petah Tikva</t>
+          <t>Pardes Hanna-Karkur</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="D29" t="n">
-        <v>2669</v>
+        <v>1569</v>
       </c>
       <c r="E29" t="n">
-        <v>5810</v>
+        <v>3402</v>
       </c>
       <c r="F29" t="n">
-        <v>7080</v>
+        <v>4485</v>
       </c>
       <c r="G29" t="n">
-        <v>10827</v>
+        <v>6617</v>
       </c>
       <c r="H29" t="n">
-        <v>12202</v>
+        <v>8795</v>
       </c>
       <c r="I29" t="n">
-        <v>9193</v>
+        <v>7227</v>
       </c>
       <c r="J29" t="n">
-        <v>7214</v>
+        <v>5531</v>
       </c>
       <c r="K29" t="n">
-        <v>5146</v>
+        <v>3441</v>
       </c>
       <c r="L29" t="n">
-        <v>4295</v>
+        <v>2434</v>
       </c>
       <c r="M29" t="n">
-        <v>1292</v>
+        <v>688</v>
       </c>
       <c r="N29" t="n">
-        <v>110</v>
+        <v>131</v>
       </c>
       <c r="O29" t="n">
-        <v>5</v>
+        <v>27</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RAN</t>
+          <t>PTV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raanana</t>
+          <t>Petah Tikva</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>2604</v>
+        <v>0</v>
       </c>
       <c r="D30" t="n">
-        <v>2919</v>
+        <v>2669</v>
       </c>
       <c r="E30" t="n">
-        <v>2821</v>
+        <v>5810</v>
       </c>
       <c r="F30" t="n">
-        <v>3871</v>
+        <v>7080</v>
       </c>
       <c r="G30" t="n">
-        <v>7379</v>
+        <v>10827</v>
       </c>
       <c r="H30" t="n">
-        <v>9475</v>
+        <v>12202</v>
       </c>
       <c r="I30" t="n">
-        <v>7486</v>
+        <v>9193</v>
       </c>
       <c r="J30" t="n">
-        <v>5297</v>
+        <v>7214</v>
       </c>
       <c r="K30" t="n">
-        <v>3081</v>
+        <v>5146</v>
       </c>
       <c r="L30" t="n">
-        <v>2077</v>
+        <v>4295</v>
       </c>
       <c r="M30" t="n">
-        <v>559</v>
+        <v>1292</v>
       </c>
       <c r="N30" t="n">
-        <v>49</v>
+        <v>110</v>
       </c>
       <c r="O30" t="n">
-        <v>24</v>
+        <v>5</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RHT</t>
+          <t>RAN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rahat</t>
+          <t>Raanana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>2205</v>
+        <v>2604</v>
       </c>
       <c r="D31" t="n">
-        <v>2244</v>
+        <v>2919</v>
       </c>
       <c r="E31" t="n">
-        <v>2115</v>
+        <v>2821</v>
       </c>
       <c r="F31" t="n">
-        <v>2504</v>
+        <v>3871</v>
       </c>
       <c r="G31" t="n">
-        <v>3145</v>
+        <v>7379</v>
       </c>
       <c r="H31" t="n">
-        <v>2471</v>
+        <v>9475</v>
       </c>
       <c r="I31" t="n">
-        <v>1449</v>
+        <v>7486</v>
       </c>
       <c r="J31" t="n">
-        <v>855</v>
+        <v>5297</v>
       </c>
       <c r="K31" t="n">
-        <v>496</v>
+        <v>3081</v>
       </c>
       <c r="L31" t="n">
-        <v>333</v>
+        <v>2077</v>
       </c>
       <c r="M31" t="n">
-        <v>109</v>
+        <v>559</v>
       </c>
       <c r="N31" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="O31" t="n">
-        <v>3</v>
+        <v>24</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RHV</t>
+          <t>RHT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rehovot</t>
+          <t>Rahat</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>12</v>
+        <v>2205</v>
       </c>
       <c r="D32" t="n">
-        <v>3517</v>
+        <v>2244</v>
       </c>
       <c r="E32" t="n">
-        <v>7675</v>
+        <v>2115</v>
       </c>
       <c r="F32" t="n">
-        <v>10843</v>
+        <v>2504</v>
       </c>
       <c r="G32" t="n">
-        <v>17911</v>
+        <v>3145</v>
       </c>
       <c r="H32" t="n">
-        <v>15746</v>
+        <v>2471</v>
       </c>
       <c r="I32" t="n">
-        <v>10127</v>
+        <v>1449</v>
       </c>
       <c r="J32" t="n">
-        <v>6779</v>
+        <v>855</v>
       </c>
       <c r="K32" t="n">
-        <v>3699</v>
+        <v>496</v>
       </c>
       <c r="L32" t="n">
-        <v>3459</v>
+        <v>333</v>
       </c>
       <c r="M32" t="n">
-        <v>1169</v>
+        <v>109</v>
       </c>
       <c r="N32" t="n">
-        <v>253</v>
+        <v>0</v>
       </c>
       <c r="O32" t="n">
-        <v>22</v>
+        <v>3</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RLZ</t>
+          <t>RHV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rishon LeZion</t>
+          <t>Rehovot</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>17947</v>
+        <v>12</v>
       </c>
       <c r="D33" t="n">
-        <v>18941</v>
+        <v>3517</v>
       </c>
       <c r="E33" t="n">
-        <v>16993</v>
+        <v>7675</v>
       </c>
       <c r="F33" t="n">
-        <v>19779</v>
+        <v>10843</v>
       </c>
       <c r="G33" t="n">
-        <v>28748</v>
+        <v>17911</v>
       </c>
       <c r="H33" t="n">
-        <v>32682</v>
+        <v>15746</v>
       </c>
       <c r="I33" t="n">
-        <v>25165</v>
+        <v>10127</v>
       </c>
       <c r="J33" t="n">
-        <v>18727</v>
+        <v>6779</v>
       </c>
       <c r="K33" t="n">
-        <v>13056</v>
+        <v>3699</v>
       </c>
       <c r="L33" t="n">
-        <v>9782</v>
+        <v>3459</v>
       </c>
       <c r="M33" t="n">
-        <v>2900</v>
+        <v>1169</v>
       </c>
       <c r="N33" t="n">
-        <v>201</v>
+        <v>253</v>
       </c>
       <c r="O33" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RMG</t>
+          <t>RLZ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ramat Gan</t>
+          <t>Rishon LeZion</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>4912</v>
+        <v>17947</v>
       </c>
       <c r="D34" t="n">
-        <v>7495</v>
+        <v>18941</v>
       </c>
       <c r="E34" t="n">
-        <v>9687</v>
+        <v>16993</v>
       </c>
       <c r="F34" t="n">
-        <v>11696</v>
+        <v>19779</v>
       </c>
       <c r="G34" t="n">
-        <v>18099</v>
+        <v>28748</v>
       </c>
       <c r="H34" t="n">
-        <v>22439</v>
+        <v>32682</v>
       </c>
       <c r="I34" t="n">
-        <v>19701</v>
+        <v>25165</v>
       </c>
       <c r="J34" t="n">
-        <v>14483</v>
+        <v>18727</v>
       </c>
       <c r="K34" t="n">
-        <v>10973</v>
+        <v>13056</v>
       </c>
       <c r="L34" t="n">
-        <v>10351</v>
+        <v>9782</v>
       </c>
       <c r="M34" t="n">
-        <v>3041</v>
+        <v>2900</v>
       </c>
       <c r="N34" t="n">
-        <v>663</v>
+        <v>201</v>
       </c>
       <c r="O34" t="n">
-        <v>72</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>RMG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ramla</t>
+          <t>Ramat Gan</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>3745</v>
+        <v>4912</v>
       </c>
       <c r="D35" t="n">
-        <v>3874</v>
+        <v>7495</v>
       </c>
       <c r="E35" t="n">
-        <v>3473</v>
+        <v>9687</v>
       </c>
       <c r="F35" t="n">
-        <v>4099</v>
+        <v>11696</v>
       </c>
       <c r="G35" t="n">
-        <v>5420</v>
+        <v>18099</v>
       </c>
       <c r="H35" t="n">
-        <v>5589</v>
+        <v>22439</v>
       </c>
       <c r="I35" t="n">
-        <v>4357</v>
+        <v>19701</v>
       </c>
       <c r="J35" t="n">
-        <v>3428</v>
+        <v>14483</v>
       </c>
       <c r="K35" t="n">
-        <v>1975</v>
+        <v>10973</v>
       </c>
       <c r="L35" t="n">
-        <v>2048</v>
+        <v>10351</v>
       </c>
       <c r="M35" t="n">
-        <v>564</v>
+        <v>3041</v>
       </c>
       <c r="N35" t="n">
-        <v>30</v>
+        <v>663</v>
       </c>
       <c r="O35" t="n">
-        <v>0</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RSN</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rosh HaAyin</t>
+          <t>Ramla</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>4205</v>
+        <v>3745</v>
       </c>
       <c r="D36" t="n">
-        <v>4753</v>
+        <v>3874</v>
       </c>
       <c r="E36" t="n">
-        <v>4778</v>
+        <v>3473</v>
       </c>
       <c r="F36" t="n">
+        <v>4099</v>
+      </c>
+      <c r="G36" t="n">
+        <v>5420</v>
+      </c>
+      <c r="H36" t="n">
         <v>5589</v>
       </c>
-      <c r="G36" t="n">
-        <v>7656</v>
-      </c>
-      <c r="H36" t="n">
-        <v>8070</v>
-      </c>
       <c r="I36" t="n">
-        <v>6223</v>
+        <v>4357</v>
       </c>
       <c r="J36" t="n">
-        <v>4466</v>
+        <v>3428</v>
       </c>
       <c r="K36" t="n">
-        <v>2886</v>
+        <v>1975</v>
       </c>
       <c r="L36" t="n">
-        <v>1720</v>
+        <v>2048</v>
       </c>
       <c r="M36" t="n">
-        <v>515</v>
+        <v>564</v>
       </c>
       <c r="N36" t="n">
-        <v>129</v>
+        <v>30</v>
       </c>
       <c r="O36" t="n">
         <v>0</v>
@@ -5907,204 +5996,255 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SDR</t>
+          <t>RSN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sderot</t>
+          <t>Rosh HaAyin</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>2793</v>
+        <v>4205</v>
       </c>
       <c r="D37" t="n">
-        <v>2890</v>
+        <v>4753</v>
       </c>
       <c r="E37" t="n">
-        <v>2559</v>
+        <v>4778</v>
       </c>
       <c r="F37" t="n">
-        <v>2722</v>
+        <v>5589</v>
       </c>
       <c r="G37" t="n">
-        <v>2794</v>
+        <v>7656</v>
       </c>
       <c r="H37" t="n">
-        <v>2334</v>
+        <v>8070</v>
       </c>
       <c r="I37" t="n">
-        <v>1881</v>
+        <v>6223</v>
       </c>
       <c r="J37" t="n">
-        <v>1738</v>
+        <v>4466</v>
       </c>
       <c r="K37" t="n">
-        <v>1197</v>
+        <v>2886</v>
       </c>
       <c r="L37" t="n">
-        <v>1610</v>
+        <v>1720</v>
       </c>
       <c r="M37" t="n">
-        <v>1036</v>
+        <v>515</v>
       </c>
       <c r="N37" t="n">
-        <v>294</v>
+        <v>129</v>
       </c>
       <c r="O37" t="n">
-        <v>201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>SDR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Sderot</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>15273</v>
+        <v>2793</v>
       </c>
       <c r="D38" t="n">
-        <v>15813</v>
+        <v>2890</v>
       </c>
       <c r="E38" t="n">
-        <v>14267</v>
+        <v>2559</v>
       </c>
       <c r="F38" t="n">
-        <v>17095</v>
+        <v>2722</v>
       </c>
       <c r="G38" t="n">
-        <v>24929</v>
+        <v>2794</v>
       </c>
       <c r="H38" t="n">
-        <v>29188</v>
+        <v>2334</v>
       </c>
       <c r="I38" t="n">
-        <v>28957</v>
+        <v>1881</v>
       </c>
       <c r="J38" t="n">
-        <v>23127</v>
+        <v>1738</v>
       </c>
       <c r="K38" t="n">
-        <v>17335</v>
+        <v>1197</v>
       </c>
       <c r="L38" t="n">
-        <v>18218</v>
+        <v>1610</v>
       </c>
       <c r="M38" t="n">
-        <v>6734</v>
+        <v>1036</v>
       </c>
       <c r="N38" t="n">
-        <v>969</v>
+        <v>294</v>
       </c>
       <c r="O38" t="n">
-        <v>194</v>
+        <v>201</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UMF</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Umm al-Fahm</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>0</v>
+        <v>15273</v>
       </c>
       <c r="D39" t="n">
-        <v>3223</v>
+        <v>15813</v>
       </c>
       <c r="E39" t="n">
-        <v>7515</v>
+        <v>14267</v>
       </c>
       <c r="F39" t="n">
-        <v>9640</v>
+        <v>17095</v>
       </c>
       <c r="G39" t="n">
-        <v>14615</v>
+        <v>24929</v>
       </c>
       <c r="H39" t="n">
-        <v>13651</v>
+        <v>29188</v>
       </c>
       <c r="I39" t="n">
-        <v>9756</v>
+        <v>28957</v>
       </c>
       <c r="J39" t="n">
-        <v>3877</v>
+        <v>23127</v>
       </c>
       <c r="K39" t="n">
-        <v>1389</v>
+        <v>17335</v>
       </c>
       <c r="L39" t="n">
-        <v>1161</v>
+        <v>18218</v>
       </c>
       <c r="M39" t="n">
-        <v>220</v>
+        <v>6734</v>
       </c>
       <c r="N39" t="n">
-        <v>82</v>
+        <v>969</v>
       </c>
       <c r="O39" t="n">
-        <v>15</v>
+        <v>194</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>UMF</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Umm al-Fahm</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" t="n">
+        <v>3223</v>
+      </c>
+      <c r="E40" t="n">
+        <v>7515</v>
+      </c>
+      <c r="F40" t="n">
+        <v>9640</v>
+      </c>
+      <c r="G40" t="n">
+        <v>14615</v>
+      </c>
+      <c r="H40" t="n">
+        <v>13651</v>
+      </c>
+      <c r="I40" t="n">
+        <v>9756</v>
+      </c>
+      <c r="J40" t="n">
+        <v>3877</v>
+      </c>
+      <c r="K40" t="n">
+        <v>1389</v>
+      </c>
+      <c r="L40" t="n">
+        <v>1161</v>
+      </c>
+      <c r="M40" t="n">
+        <v>220</v>
+      </c>
+      <c r="N40" t="n">
+        <v>82</v>
+      </c>
+      <c r="O40" t="n">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>YVN</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Yavne</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C41" t="n">
         <v>5268</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>5077</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>4393</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>5109</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>6850</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>6977</v>
       </c>
-      <c r="I40" t="n">
+      <c r="I41" t="n">
         <v>5372</v>
       </c>
-      <c r="J40" t="n">
+      <c r="J41" t="n">
         <v>4724</v>
       </c>
-      <c r="K40" t="n">
+      <c r="K41" t="n">
         <v>2101</v>
       </c>
-      <c r="L40" t="n">
+      <c r="L41" t="n">
         <v>1534</v>
       </c>
-      <c r="M40" t="n">
+      <c r="M41" t="n">
         <v>625</v>
       </c>
-      <c r="N40" t="n">
+      <c r="N41" t="n">
         <v>68</v>
       </c>
-      <c r="O40" t="n">
+      <c r="O41" t="n">
         <v>11</v>
       </c>
     </row>
@@ -6119,7 +6259,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H40"/>
+  <dimension ref="A1:H41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6377,960 +6517,990 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BTY</t>
+          <t>BTR</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Bat Yam</t>
+          <t>Beitar Ilit</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>31.53048225659691</v>
+        <v>29.38520580931597</v>
       </c>
       <c r="D9" t="n">
-        <v>20.77525022747953</v>
+        <v>43.35916923771541</v>
       </c>
       <c r="E9" t="n">
-        <v>24.71337579617834</v>
+        <v>20.49815636993002</v>
       </c>
       <c r="F9" t="n">
-        <v>15.6869881710646</v>
+        <v>5.40296485815336</v>
       </c>
       <c r="G9" t="n">
-        <v>7.155595996360327</v>
+        <v>1.354503724885243</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1383075523202912</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ELT</t>
+          <t>BTY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Eilat</t>
+          <t>Bat Yam</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>18.98979363778589</v>
+        <v>31.53048225659691</v>
       </c>
       <c r="D10" t="n">
-        <v>33.4798480220517</v>
+        <v>20.77525022747953</v>
       </c>
       <c r="E10" t="n">
-        <v>29.06950756164792</v>
+        <v>24.71337579617834</v>
       </c>
       <c r="F10" t="n">
-        <v>13.29062057662222</v>
+        <v>15.6869881710646</v>
       </c>
       <c r="G10" t="n">
-        <v>5.170230201892275</v>
+        <v>7.155595996360327</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>0.1383075523202912</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>ELT</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Givatayim</t>
+          <t>Eilat</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>18.98709727265704</v>
+        <v>18.98979363778589</v>
       </c>
       <c r="D11" t="n">
-        <v>21.81874372247547</v>
+        <v>33.4798480220517</v>
       </c>
       <c r="E11" t="n">
-        <v>30.39094491230781</v>
+        <v>29.06950756164792</v>
       </c>
       <c r="F11" t="n">
-        <v>18.75917484354477</v>
+        <v>13.29062057662222</v>
       </c>
       <c r="G11" t="n">
-        <v>9.684771691261686</v>
+        <v>5.170230201892275</v>
       </c>
       <c r="H11" t="n">
-        <v>0.3592675577532257</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>HAI</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Haifa</t>
+          <t>Givatayim</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>19.32378136608293</v>
+        <v>18.98709727265704</v>
       </c>
       <c r="D12" t="n">
-        <v>17.23144568266242</v>
+        <v>21.81874372247547</v>
       </c>
       <c r="E12" t="n">
-        <v>26.70760366916837</v>
+        <v>30.39094491230781</v>
       </c>
       <c r="F12" t="n">
-        <v>21.84317590276198</v>
+        <v>18.75917484354477</v>
       </c>
       <c r="G12" t="n">
-        <v>14.53137240037399</v>
+        <v>9.684771691261686</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3626209789502944</v>
+        <v>0.3592675577532257</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HDR</t>
+          <t>HAI</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Hadera</t>
+          <t>Haifa</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>19.43787330849897</v>
+        <v>19.32378136608293</v>
       </c>
       <c r="D13" t="n">
-        <v>24.47544207883551</v>
+        <v>17.23144568266242</v>
       </c>
       <c r="E13" t="n">
-        <v>25.72350472668606</v>
+        <v>26.70760366916837</v>
       </c>
       <c r="F13" t="n">
-        <v>16.66530712129864</v>
+        <v>21.84317590276198</v>
       </c>
       <c r="G13" t="n">
-        <v>12.96915644741732</v>
+        <v>14.53137240037399</v>
       </c>
       <c r="H13" t="n">
-        <v>0.7287163172635071</v>
+        <v>0.3626209789502944</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>HDS</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Hod HaSharon</t>
+          <t>Hadera</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>10.69077086680091</v>
+        <v>19.43787330849897</v>
       </c>
       <c r="D14" t="n">
-        <v>24.55822793402267</v>
+        <v>24.47544207883551</v>
       </c>
       <c r="E14" t="n">
-        <v>39.4551666402697</v>
+        <v>25.72350472668606</v>
       </c>
       <c r="F14" t="n">
-        <v>18.56913365160531</v>
+        <v>16.66530712129864</v>
       </c>
       <c r="G14" t="n">
-        <v>6.509491594452112</v>
+        <v>12.96915644741732</v>
       </c>
       <c r="H14" t="n">
-        <v>0.2172093128492884</v>
+        <v>0.7287163172635071</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>HOL</t>
+          <t>HDS</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Holon</t>
+          <t>Hod HaSharon</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>27.69957365480741</v>
+        <v>10.69077086680091</v>
       </c>
       <c r="D15" t="n">
-        <v>22.5705674801529</v>
+        <v>24.55822793402267</v>
       </c>
       <c r="E15" t="n">
-        <v>25.17825639517789</v>
+        <v>39.4551666402697</v>
       </c>
       <c r="F15" t="n">
-        <v>17.40480740958542</v>
+        <v>18.56913365160531</v>
       </c>
       <c r="G15" t="n">
-        <v>7.144957365480741</v>
+        <v>6.509491594452112</v>
       </c>
       <c r="H15" t="n">
-        <v>0.001837694795648339</v>
+        <v>0.2172093128492884</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HRZ</t>
+          <t>HOL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Herzliya</t>
+          <t>Holon</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>19.78383331985661</v>
+        <v>27.69957365480741</v>
       </c>
       <c r="D16" t="n">
-        <v>20.44284520632867</v>
+        <v>22.5705674801529</v>
       </c>
       <c r="E16" t="n">
-        <v>33.39936928923748</v>
+        <v>25.17825639517789</v>
       </c>
       <c r="F16" t="n">
-        <v>18.51567343198296</v>
+        <v>17.40480740958542</v>
       </c>
       <c r="G16" t="n">
-        <v>7.677690628284951</v>
+        <v>7.144957365480741</v>
       </c>
       <c r="H16" t="n">
-        <v>0.1805881243093178</v>
+        <v>0.001837694795648339</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>JER</t>
+          <t>HRZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Jerusalem</t>
+          <t>Herzliya</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>32.02979014872312</v>
+        <v>19.78383331985661</v>
       </c>
       <c r="D17" t="n">
-        <v>25.68355313121447</v>
+        <v>20.44284520632867</v>
       </c>
       <c r="E17" t="n">
-        <v>27.14471067590694</v>
+        <v>33.39936928923748</v>
       </c>
       <c r="F17" t="n">
-        <v>12.12154446897756</v>
+        <v>18.51567343198296</v>
       </c>
       <c r="G17" t="n">
-        <v>3.018125306520268</v>
+        <v>7.677690628284951</v>
       </c>
       <c r="H17" t="n">
-        <v>0.002276268657642986</v>
+        <v>0.1805881243093178</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KAT</t>
+          <t>JER</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Kiryat Ata</t>
+          <t>Jerusalem</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>18.24967310765654</v>
+        <v>32.02979014872312</v>
       </c>
       <c r="D18" t="n">
-        <v>26.3420746767398</v>
+        <v>25.68355313121447</v>
       </c>
       <c r="E18" t="n">
-        <v>30.60620369025134</v>
+        <v>27.14471067590694</v>
       </c>
       <c r="F18" t="n">
-        <v>16.96208048815923</v>
+        <v>12.12154446897756</v>
       </c>
       <c r="G18" t="n">
-        <v>7.267906436147029</v>
+        <v>3.018125306520268</v>
       </c>
       <c r="H18" t="n">
-        <v>0.5720616010460555</v>
+        <v>0.002276268657642986</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>KFS</t>
+          <t>KAT</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Kfar Saba</t>
+          <t>Kiryat Ata</t>
         </is>
       </c>
       <c r="C19" t="n">
-        <v>20.30289727831431</v>
+        <v>18.24967310765654</v>
       </c>
       <c r="D19" t="n">
-        <v>20.63944980977466</v>
+        <v>26.3420746767398</v>
       </c>
       <c r="E19" t="n">
-        <v>33.27663154814164</v>
+        <v>30.60620369025134</v>
       </c>
       <c r="F19" t="n">
-        <v>17.92873865964296</v>
+        <v>16.96208048815923</v>
       </c>
       <c r="G19" t="n">
-        <v>7.490122914837577</v>
+        <v>7.267906436147029</v>
       </c>
       <c r="H19" t="n">
-        <v>0.3621597892888498</v>
+        <v>0.5720616010460555</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>KGT</t>
+          <t>KFS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Kiryat Gat</t>
+          <t>Kfar Saba</t>
         </is>
       </c>
       <c r="C20" t="n">
-        <v>30.59088767750185</v>
+        <v>20.30289727831431</v>
       </c>
       <c r="D20" t="n">
-        <v>25.91695268860623</v>
+        <v>20.63944980977466</v>
       </c>
       <c r="E20" t="n">
-        <v>22.12463826637055</v>
+        <v>33.27663154814164</v>
       </c>
       <c r="F20" t="n">
-        <v>14.33811158220607</v>
+        <v>17.92873865964296</v>
       </c>
       <c r="G20" t="n">
-        <v>6.86452654956592</v>
+        <v>7.490122914837577</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1648832357493775</v>
+        <v>0.3621597892888498</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>LOD</t>
+          <t>KGT</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Lod</t>
+          <t>Kiryat Gat</t>
         </is>
       </c>
       <c r="C21" t="n">
-        <v>29.89699149771092</v>
+        <v>30.59088767750185</v>
       </c>
       <c r="D21" t="n">
-        <v>26.42249836494441</v>
+        <v>25.91695268860623</v>
       </c>
       <c r="E21" t="n">
-        <v>25.86112927839547</v>
+        <v>22.12463826637055</v>
       </c>
       <c r="F21" t="n">
-        <v>12.5327011118378</v>
+        <v>14.33811158220607</v>
       </c>
       <c r="G21" t="n">
-        <v>5.237628079354698</v>
+        <v>6.86452654956592</v>
       </c>
       <c r="H21" t="n">
-        <v>0.04905166775670373</v>
+        <v>0.1648832357493775</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>MDN</t>
+          <t>LOD</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Modiin</t>
+          <t>Lod</t>
         </is>
       </c>
       <c r="C22" t="n">
-        <v>15.78086445424048</v>
+        <v>29.89699149771092</v>
       </c>
       <c r="D22" t="n">
-        <v>32.17305719593002</v>
+        <v>26.42249836494441</v>
       </c>
       <c r="E22" t="n">
-        <v>34.42568410546453</v>
+        <v>25.86112927839547</v>
       </c>
       <c r="F22" t="n">
-        <v>13.29812304194738</v>
+        <v>12.5327011118378</v>
       </c>
       <c r="G22" t="n">
-        <v>4.29454656353101</v>
+        <v>5.237628079354698</v>
       </c>
       <c r="H22" t="n">
-        <v>0.0277246388865785</v>
+        <v>0.04905166775670373</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>NHR</t>
+          <t>MDN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Nahariya</t>
+          <t>Modiin</t>
         </is>
       </c>
       <c r="C23" t="n">
-        <v>15.29671120709047</v>
+        <v>15.78086445424048</v>
       </c>
       <c r="D23" t="n">
-        <v>28.98276870472849</v>
+        <v>32.17305719593002</v>
       </c>
       <c r="E23" t="n">
-        <v>31.01183245602195</v>
+        <v>34.42568410546453</v>
       </c>
       <c r="F23" t="n">
-        <v>15.9355738516219</v>
+        <v>13.29812304194738</v>
       </c>
       <c r="G23" t="n">
-        <v>8.45818149097944</v>
+        <v>4.29454656353101</v>
       </c>
       <c r="H23" t="n">
-        <v>0.314932289557745</v>
+        <v>0.0277246388865785</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>NSZ</t>
+          <t>NHR</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Ness Ziona</t>
+          <t>Nahariya</t>
         </is>
       </c>
       <c r="C24" t="n">
-        <v>15.27473358022825</v>
+        <v>15.29671120709047</v>
       </c>
       <c r="D24" t="n">
-        <v>37.11233718791726</v>
+        <v>28.98276870472849</v>
       </c>
       <c r="E24" t="n">
-        <v>31.40856070339859</v>
+        <v>31.01183245602195</v>
       </c>
       <c r="F24" t="n">
-        <v>12.01219358577079</v>
+        <v>15.9355738516219</v>
       </c>
       <c r="G24" t="n">
-        <v>4.179578263169828</v>
+        <v>8.45818149097944</v>
       </c>
       <c r="H24" t="n">
-        <v>0.01259667951527977</v>
+        <v>0.314932289557745</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>NTN</t>
+          <t>NSZ</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Netanya</t>
+          <t>Ness Ziona</t>
         </is>
       </c>
       <c r="C25" t="n">
-        <v>15.24941255454851</v>
+        <v>15.27473358022825</v>
       </c>
       <c r="D25" t="n">
-        <v>29.46894931184961</v>
+        <v>37.11233718791726</v>
       </c>
       <c r="E25" t="n">
-        <v>31.78784827123195</v>
+        <v>31.40856070339859</v>
       </c>
       <c r="F25" t="n">
-        <v>15.48707620006714</v>
+        <v>12.01219358577079</v>
       </c>
       <c r="G25" t="n">
-        <v>7.610607586438402</v>
+        <v>4.179578263169828</v>
       </c>
       <c r="H25" t="n">
-        <v>0.396106075864384</v>
+        <v>0.01259667951527977</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NTV</t>
+          <t>NTN</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Netivot</t>
+          <t>Netanya</t>
         </is>
       </c>
       <c r="C26" t="n">
-        <v>35.20908301278074</v>
+        <v>15.24941255454851</v>
       </c>
       <c r="D26" t="n">
-        <v>23.46444968358357</v>
+        <v>29.46894931184961</v>
       </c>
       <c r="E26" t="n">
-        <v>22.09951606899119</v>
+        <v>31.78784827123195</v>
       </c>
       <c r="F26" t="n">
-        <v>12.817967489763</v>
+        <v>15.48707620006714</v>
       </c>
       <c r="G26" t="n">
-        <v>6.291103114530339</v>
+        <v>7.610607586438402</v>
       </c>
       <c r="H26" t="n">
-        <v>0.1178806303511602</v>
+        <v>0.396106075864384</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NZR</t>
+          <t>NTV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nazareth</t>
+          <t>Netivot</t>
         </is>
       </c>
       <c r="C27" t="n">
-        <v>18.92590968873301</v>
+        <v>35.20908301278074</v>
       </c>
       <c r="D27" t="n">
-        <v>34.68434896975011</v>
+        <v>23.46444968358357</v>
       </c>
       <c r="E27" t="n">
-        <v>32.66330556773345</v>
+        <v>22.09951606899119</v>
       </c>
       <c r="F27" t="n">
-        <v>10.67075843928102</v>
+        <v>12.817967489763</v>
       </c>
       <c r="G27" t="n">
-        <v>2.996492766330557</v>
+        <v>6.291103114530339</v>
       </c>
       <c r="H27" t="n">
-        <v>0.05918456817185445</v>
+        <v>0.1178806303511602</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PHK</t>
+          <t>NZR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pardes Hanna-Karkur</t>
+          <t>Nazareth</t>
         </is>
       </c>
       <c r="C28" t="n">
-        <v>11.21200513733354</v>
+        <v>18.92590968873301</v>
       </c>
       <c r="D28" t="n">
-        <v>25.01520921114891</v>
+        <v>34.68434896975011</v>
       </c>
       <c r="E28" t="n">
-        <v>36.10103422635812</v>
+        <v>32.66330556773345</v>
       </c>
       <c r="F28" t="n">
-        <v>20.21585813749127</v>
+        <v>10.67075843928102</v>
       </c>
       <c r="G28" t="n">
-        <v>7.034541808431537</v>
+        <v>2.996492766330557</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4213514792366102</v>
+        <v>0.05918456817185445</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>PTV</t>
+          <t>PHK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Petah Tikva</t>
+          <t>Pardes Hanna-Karkur</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>12.87623386484434</v>
+        <v>11.21200513733354</v>
       </c>
       <c r="D29" t="n">
-        <v>27.19362186788155</v>
+        <v>25.01520921114891</v>
       </c>
       <c r="E29" t="n">
-        <v>32.49050873196659</v>
+        <v>36.10103422635812</v>
       </c>
       <c r="F29" t="n">
-        <v>18.76993166287016</v>
+        <v>20.21585813749127</v>
       </c>
       <c r="G29" t="n">
-        <v>8.484434320425208</v>
+        <v>7.034541808431537</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1852695520121488</v>
+        <v>0.4213514792366102</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>RAN</t>
+          <t>PTV</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Raanana</t>
+          <t>Petah Tikva</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>17.51395827211284</v>
+        <v>12.87623386484434</v>
       </c>
       <c r="D30" t="n">
-        <v>23.61361823601024</v>
+        <v>27.19362186788155</v>
       </c>
       <c r="E30" t="n">
-        <v>35.60094034675286</v>
+        <v>32.49050873196659</v>
       </c>
       <c r="F30" t="n">
-        <v>17.58532387389278</v>
+        <v>18.76993166287016</v>
       </c>
       <c r="G30" t="n">
-        <v>5.532933126233155</v>
+        <v>8.484434320425208</v>
       </c>
       <c r="H30" t="n">
-        <v>0.1532261449981109</v>
+        <v>0.1852695520121488</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>RHT</t>
+          <t>RAN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Rahat</t>
+          <t>Raanana</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>36.61107702604718</v>
+        <v>17.51395827211284</v>
       </c>
       <c r="D31" t="n">
-        <v>31.50761336382397</v>
+        <v>23.61361823601024</v>
       </c>
       <c r="E31" t="n">
-        <v>21.86401918679235</v>
+        <v>35.60094034675286</v>
       </c>
       <c r="F31" t="n">
-        <v>7.535278041162363</v>
+        <v>17.58532387389278</v>
       </c>
       <c r="G31" t="n">
-        <v>2.465279714429137</v>
+        <v>5.532933126233155</v>
       </c>
       <c r="H31" t="n">
-        <v>0.01673266774499415</v>
+        <v>0.1532261449981109</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>RHV</t>
+          <t>RHT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Rehovot</t>
+          <t>Rahat</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>13.7958208661175</v>
+        <v>36.61107702604718</v>
       </c>
       <c r="D32" t="n">
-        <v>35.40566165515373</v>
+        <v>31.50761336382397</v>
       </c>
       <c r="E32" t="n">
-        <v>31.85820004186522</v>
+        <v>21.86401918679235</v>
       </c>
       <c r="F32" t="n">
-        <v>12.9018753155283</v>
+        <v>7.535278041162363</v>
       </c>
       <c r="G32" t="n">
-        <v>5.698595052516223</v>
+        <v>2.465279714429137</v>
       </c>
       <c r="H32" t="n">
-        <v>0.3398470688190314</v>
+        <v>0.01673266774499415</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>RLZ</t>
+          <t>RHV</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Rishon LeZion</t>
+          <t>Rehovot</t>
         </is>
       </c>
       <c r="C33" t="n">
-        <v>26.29187933676208</v>
+        <v>13.7958208661175</v>
       </c>
       <c r="D33" t="n">
-        <v>23.67933090653576</v>
+        <v>35.40566165515373</v>
       </c>
       <c r="E33" t="n">
-        <v>28.22713654152069</v>
+        <v>31.85820004186522</v>
       </c>
       <c r="F33" t="n">
-        <v>15.50889554685899</v>
+        <v>12.9018753155283</v>
       </c>
       <c r="G33" t="n">
-        <v>6.188333805029912</v>
+        <v>5.698595052516223</v>
       </c>
       <c r="H33" t="n">
-        <v>0.1044238632925722</v>
+        <v>0.3398470688190314</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>RMG</t>
+          <t>RLZ</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Ramat Gan</t>
+          <t>Rishon LeZion</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>16.53482611266193</v>
+        <v>26.29187933676208</v>
       </c>
       <c r="D34" t="n">
-        <v>22.29814175915462</v>
+        <v>23.67933090653576</v>
       </c>
       <c r="E34" t="n">
-        <v>31.53695901093391</v>
+        <v>28.22713654152069</v>
       </c>
       <c r="F34" t="n">
-        <v>19.05089768823763</v>
+        <v>15.50889554685899</v>
       </c>
       <c r="G34" t="n">
-        <v>10.02237672222181</v>
+        <v>6.188333805029912</v>
       </c>
       <c r="H34" t="n">
-        <v>0.5567987067901004</v>
+        <v>0.1044238632925722</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>RML</t>
+          <t>RMG</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Ramla</t>
+          <t>Ramat Gan</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>28.73426247344697</v>
+        <v>16.53482611266193</v>
       </c>
       <c r="D35" t="n">
-        <v>24.65934407543651</v>
+        <v>22.29814175915462</v>
       </c>
       <c r="E35" t="n">
-        <v>25.7655043780115</v>
+        <v>31.53695901093391</v>
       </c>
       <c r="F35" t="n">
-        <v>13.99668410963162</v>
+        <v>19.05089768823763</v>
       </c>
       <c r="G35" t="n">
-        <v>6.766488782964614</v>
+        <v>10.02237672222181</v>
       </c>
       <c r="H35" t="n">
-        <v>0.07771618050878193</v>
+        <v>0.5567987067901004</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>RSN</t>
+          <t>RML</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Rosh HaAyin</t>
+          <t>Ramla</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>26.93861541478721</v>
+        <v>28.73426247344697</v>
       </c>
       <c r="D36" t="n">
-        <v>25.97568150617768</v>
+        <v>24.65934407543651</v>
       </c>
       <c r="E36" t="n">
-        <v>28.03098646793489</v>
+        <v>25.7655043780115</v>
       </c>
       <c r="F36" t="n">
-        <v>14.41851343400667</v>
+        <v>13.99668410963162</v>
       </c>
       <c r="G36" t="n">
-        <v>4.383212394587174</v>
+        <v>6.766488782964614</v>
       </c>
       <c r="H36" t="n">
-        <v>0.2529907825063738</v>
+        <v>0.07771618050878193</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SDR</t>
+          <t>RSN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Sderot</t>
+          <t>Rosh HaAyin</t>
         </is>
       </c>
       <c r="C37" t="n">
-        <v>34.20768656096953</v>
+        <v>26.93861541478721</v>
       </c>
       <c r="D37" t="n">
-        <v>22.89366647298083</v>
+        <v>25.97568150617768</v>
       </c>
       <c r="E37" t="n">
-        <v>17.49398190420852</v>
+        <v>28.03098646793489</v>
       </c>
       <c r="F37" t="n">
-        <v>12.18145596414045</v>
+        <v>14.41851343400667</v>
       </c>
       <c r="G37" t="n">
-        <v>10.98198721673446</v>
+        <v>4.383212394587174</v>
       </c>
       <c r="H37" t="n">
-        <v>2.241221880966216</v>
+        <v>0.2529907825063738</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>TLV</t>
+          <t>SDR</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Tel Aviv</t>
+          <t>Sderot</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>21.38011662824629</v>
+        <v>34.20768656096953</v>
       </c>
       <c r="D38" t="n">
-        <v>19.81077373460239</v>
+        <v>22.89366647298083</v>
       </c>
       <c r="E38" t="n">
-        <v>27.41046637156043</v>
+        <v>17.49398190420852</v>
       </c>
       <c r="F38" t="n">
-        <v>19.07442239790314</v>
+        <v>12.18145596414045</v>
       </c>
       <c r="G38" t="n">
-        <v>11.76276475884729</v>
+        <v>10.98198721673446</v>
       </c>
       <c r="H38" t="n">
-        <v>0.5614561088404588</v>
+        <v>2.241221880966216</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>UMF</t>
+          <t>TLV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Umm al-Fahm</t>
+          <t>Tel Aviv</t>
         </is>
       </c>
       <c r="C39" t="n">
-        <v>16.48348274591674</v>
+        <v>21.38011662824629</v>
       </c>
       <c r="D39" t="n">
-        <v>37.23289942281715</v>
+        <v>19.81077373460239</v>
       </c>
       <c r="E39" t="n">
-        <v>35.93116787424782</v>
+        <v>27.41046637156043</v>
       </c>
       <c r="F39" t="n">
-        <v>8.083630111752425</v>
+        <v>19.07442239790314</v>
       </c>
       <c r="G39" t="n">
-        <v>2.119918948790372</v>
+        <v>11.76276475884729</v>
       </c>
       <c r="H39" t="n">
-        <v>0.1489008964755004</v>
+        <v>0.5614561088404588</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
+          <t>UMF</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Umm al-Fahm</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>16.48348274591674</v>
+      </c>
+      <c r="D40" t="n">
+        <v>37.23289942281715</v>
+      </c>
+      <c r="E40" t="n">
+        <v>35.93116787424782</v>
+      </c>
+      <c r="F40" t="n">
+        <v>8.083630111752425</v>
+      </c>
+      <c r="G40" t="n">
+        <v>2.119918948790372</v>
+      </c>
+      <c r="H40" t="n">
+        <v>0.1489008964755004</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
           <t>YVN</t>
         </is>
       </c>
-      <c r="B40" t="inlineStr">
+      <c r="B41" t="inlineStr">
         <is>
           <t>Yavne</t>
         </is>
       </c>
-      <c r="C40" t="n">
+      <c r="C41" t="n">
         <v>30.63396383288298</v>
       </c>
-      <c r="D40" t="n">
+      <c r="D41" t="n">
         <v>24.85761795884432</v>
       </c>
-      <c r="E40" t="n">
+      <c r="E41" t="n">
         <v>25.66826023695698</v>
       </c>
-      <c r="F40" t="n">
+      <c r="F41" t="n">
         <v>14.18623986697152</v>
       </c>
-      <c r="G40" t="n">
+      <c r="G41" t="n">
         <v>4.487632508833922</v>
       </c>
-      <c r="H40" t="n">
+      <c r="H41" t="n">
         <v>0.1662855955102889</v>
       </c>
     </row>
@@ -7367,7 +7537,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3074501</v>
+        <v>3087790</v>
       </c>
     </row>
     <row r="3">
@@ -7377,7 +7547,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1728663</v>
+        <v>1738574</v>
       </c>
     </row>
     <row r="4">
@@ -7387,7 +7557,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="5">
@@ -7407,7 +7577,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>6.07</v>
+        <v>6.06</v>
       </c>
     </row>
     <row r="7">
@@ -7471,7 +7641,7 @@
         <v>208462</v>
       </c>
       <c r="C2" t="n">
-        <v>6.780903706301144</v>
+        <v>6.751718196363448</v>
       </c>
     </row>
     <row r="3">
@@ -7481,10 +7651,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>249768</v>
+        <v>251050</v>
       </c>
       <c r="C3" t="n">
-        <v>8.124515532401226</v>
+        <v>8.131068747287484</v>
       </c>
     </row>
     <row r="4">
@@ -7494,10 +7664,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>272118</v>
+        <v>274741</v>
       </c>
       <c r="C4" t="n">
-        <v>8.85152188289115</v>
+        <v>8.898378644487197</v>
       </c>
     </row>
     <row r="5">
@@ -7507,10 +7677,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>320876</v>
+        <v>323781</v>
       </c>
       <c r="C5" t="n">
-        <v>10.43753421565123</v>
+        <v>10.48669814804019</v>
       </c>
     </row>
     <row r="6">
@@ -7520,10 +7690,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>454045</v>
+        <v>456902</v>
       </c>
       <c r="C6" t="n">
-        <v>14.76928851938245</v>
+        <v>14.79825362586396</v>
       </c>
     </row>
     <row r="7">
@@ -7533,10 +7703,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>488985</v>
+        <v>490908</v>
       </c>
       <c r="C7" t="n">
-        <v>15.90582551652419</v>
+        <v>15.89964826366622</v>
       </c>
     </row>
     <row r="8">
@@ -7546,10 +7716,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>393897</v>
+        <v>394698</v>
       </c>
       <c r="C8" t="n">
-        <v>12.81277943798343</v>
+        <v>12.78357527351872</v>
       </c>
     </row>
     <row r="9">
@@ -7559,10 +7729,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>286608</v>
+        <v>287096</v>
       </c>
       <c r="C9" t="n">
-        <v>9.322856201396698</v>
+        <v>9.298535403589913</v>
       </c>
     </row>
     <row r="10">
@@ -7572,10 +7742,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>181039</v>
+        <v>181269</v>
       </c>
       <c r="C10" t="n">
-        <v>5.888881551961762</v>
+        <v>5.870984667405119</v>
       </c>
     </row>
     <row r="11">
@@ -7585,10 +7755,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>154716</v>
+        <v>154867</v>
       </c>
       <c r="C11" t="n">
-        <v>5.032640470800855</v>
+        <v>5.015870239737785</v>
       </c>
     </row>
     <row r="12">
@@ -7598,10 +7768,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>56482</v>
+        <v>56511</v>
       </c>
       <c r="C12" t="n">
-        <v>1.83726052296966</v>
+        <v>1.830292077187664</v>
       </c>
     </row>
     <row r="13">
@@ -7614,7 +7784,7 @@
         <v>6145</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1998860860742991</v>
+        <v>0.1990257616095662</v>
       </c>
     </row>
     <row r="14">
@@ -7627,7 +7797,7 @@
         <v>1110</v>
       </c>
       <c r="C14" t="n">
-        <v>0.0361063556619157</v>
+        <v>0.03595095124273694</v>
       </c>
     </row>
   </sheetData>
